--- a/Electricity_Bill_Dummy_Data_v1.xlsx
+++ b/Electricity_Bill_Dummy_Data_v1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bcld\MSDD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bcld\documentdesigner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9367BD6-C2A5-4F63-8294-5288A711AC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37D30C6-78D2-4F13-AB30-DC181FF7700C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="83">
   <si>
     <t>RecordID</t>
   </si>
@@ -229,13 +229,67 @@
   </si>
   <si>
     <t>Pafos, Cyrpus</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>MTotAmount</t>
+  </si>
+  <si>
+    <t>M1TotAmount</t>
+  </si>
+  <si>
+    <t>M2TotAmount</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,6 +302,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -257,7 +317,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -280,13 +340,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -591,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -611,7 +685,7 @@
     <col min="16" max="16" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -660,8 +734,26 @@
       <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="Q1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -710,8 +802,26 @@
       <c r="P2" t="s">
         <v>21</v>
       </c>
+      <c r="Q2" t="s">
+        <v>71</v>
+      </c>
+      <c r="R2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S2" t="s">
+        <v>73</v>
+      </c>
+      <c r="T2">
+        <v>300</v>
+      </c>
+      <c r="U2">
+        <v>400</v>
+      </c>
+      <c r="V2">
+        <v>500</v>
+      </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -760,8 +870,26 @@
       <c r="P3" t="s">
         <v>21</v>
       </c>
+      <c r="Q3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S3" t="s">
+        <v>74</v>
+      </c>
+      <c r="T3">
+        <v>300</v>
+      </c>
+      <c r="U3">
+        <v>400</v>
+      </c>
+      <c r="V3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -810,8 +938,26 @@
       <c r="P4" t="s">
         <v>21</v>
       </c>
+      <c r="Q4" t="s">
+        <v>71</v>
+      </c>
+      <c r="R4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S4" t="s">
+        <v>75</v>
+      </c>
+      <c r="T4">
+        <v>300</v>
+      </c>
+      <c r="U4">
+        <v>400</v>
+      </c>
+      <c r="V4">
+        <v>500</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -860,8 +1006,26 @@
       <c r="P5" t="s">
         <v>21</v>
       </c>
+      <c r="Q5" t="s">
+        <v>71</v>
+      </c>
+      <c r="R5" t="s">
+        <v>72</v>
+      </c>
+      <c r="S5" t="s">
+        <v>76</v>
+      </c>
+      <c r="T5">
+        <v>300</v>
+      </c>
+      <c r="U5">
+        <v>400</v>
+      </c>
+      <c r="V5">
+        <v>500</v>
+      </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -910,8 +1074,26 @@
       <c r="P6" t="s">
         <v>21</v>
       </c>
+      <c r="Q6" t="s">
+        <v>71</v>
+      </c>
+      <c r="R6" t="s">
+        <v>72</v>
+      </c>
+      <c r="S6" t="s">
+        <v>77</v>
+      </c>
+      <c r="T6">
+        <v>300</v>
+      </c>
+      <c r="U6">
+        <v>400</v>
+      </c>
+      <c r="V6">
+        <v>500</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -960,8 +1142,26 @@
       <c r="P7" t="s">
         <v>21</v>
       </c>
+      <c r="Q7" t="s">
+        <v>71</v>
+      </c>
+      <c r="R7" t="s">
+        <v>72</v>
+      </c>
+      <c r="S7" t="s">
+        <v>78</v>
+      </c>
+      <c r="T7">
+        <v>300</v>
+      </c>
+      <c r="U7">
+        <v>400</v>
+      </c>
+      <c r="V7">
+        <v>500</v>
+      </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -1010,8 +1210,26 @@
       <c r="P8" t="s">
         <v>21</v>
       </c>
+      <c r="Q8" t="s">
+        <v>71</v>
+      </c>
+      <c r="R8" t="s">
+        <v>72</v>
+      </c>
+      <c r="S8" t="s">
+        <v>79</v>
+      </c>
+      <c r="T8">
+        <v>300</v>
+      </c>
+      <c r="U8">
+        <v>400</v>
+      </c>
+      <c r="V8">
+        <v>500</v>
+      </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -1060,8 +1278,26 @@
       <c r="P9" t="s">
         <v>21</v>
       </c>
+      <c r="Q9" t="s">
+        <v>71</v>
+      </c>
+      <c r="R9" t="s">
+        <v>72</v>
+      </c>
+      <c r="S9" t="s">
+        <v>80</v>
+      </c>
+      <c r="T9">
+        <v>300</v>
+      </c>
+      <c r="U9">
+        <v>400</v>
+      </c>
+      <c r="V9">
+        <v>500</v>
+      </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -1110,8 +1346,26 @@
       <c r="P10" t="s">
         <v>21</v>
       </c>
+      <c r="Q10" t="s">
+        <v>71</v>
+      </c>
+      <c r="R10" t="s">
+        <v>72</v>
+      </c>
+      <c r="S10" t="s">
+        <v>81</v>
+      </c>
+      <c r="T10">
+        <v>300</v>
+      </c>
+      <c r="U10">
+        <v>400</v>
+      </c>
+      <c r="V10">
+        <v>500</v>
+      </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1160,8 +1414,27 @@
       <c r="P11" t="s">
         <v>21</v>
       </c>
+      <c r="Q11" t="s">
+        <v>71</v>
+      </c>
+      <c r="R11" t="s">
+        <v>72</v>
+      </c>
+      <c r="S11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T11">
+        <v>300</v>
+      </c>
+      <c r="U11">
+        <v>400</v>
+      </c>
+      <c r="V11">
+        <v>500</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>